--- a/data/source/weekly/cs-en-us-049pct.xlsx
+++ b/data/source/weekly/cs-en-us-049pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -851,82 +851,82 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>22</v>
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>7</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="L15" s="15">
-        <v>133.333333333333</v>
+        <v>125</v>
       </c>
       <c r="M15" s="15">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="N15" s="15">
-        <v>133.333333333333</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H16" s="15">
-        <v>-32</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J16" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L16" s="15">
-        <v>-13.888888888888</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M16" s="15">
-        <v>-27.906976744186</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="N16" s="15">
-        <v>-69.607843137254</v>
+        <v>-69.747899159663</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,10 +975,10 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
         <v>50</v>
@@ -987,28 +987,28 @@
         <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>-12.121212121212</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J17" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.272727272727</v>
+        <v>4</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.510638297872</v>
+        <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>86.956521739130</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N17" s="15">
-        <v>207.142857142857</v>
+        <v>188.888888888889</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
         <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>-62.5</v>
+        <v>-25</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H18" s="15">
-        <v>-72.727272727272</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="I18" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J18" s="14">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="K18" s="15">
-        <v>-63.157894736842</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="L18" s="15">
-        <v>-26.315789473684</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M18" s="15">
-        <v>-61.111111111111</v>
+        <v>-50</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.893401015228</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E19" s="15">
-        <v>-22.222222222222</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G19" s="14">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H19" s="15">
-        <v>-8.510638297872</v>
+        <v>-15.094339622641</v>
       </c>
       <c r="I19" s="14">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="J19" s="14">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="K19" s="15">
-        <v>-25</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="L19" s="15">
-        <v>-46</v>
+        <v>-41.025641025641</v>
       </c>
       <c r="M19" s="15">
-        <v>42.105263157894</v>
+        <v>60.465116279069</v>
       </c>
       <c r="N19" s="15">
-        <v>-10</v>
+        <v>4.545454545454</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F20" s="14">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G20" s="14">
         <v>34</v>
       </c>
       <c r="H20" s="15">
-        <v>20.588235294117</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I20" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J20" s="14">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="K20" s="15">
-        <v>-7.547169811320</v>
+        <v>-17.1875</v>
       </c>
       <c r="L20" s="15">
-        <v>-5.769230769230</v>
+        <v>-14.516129032258</v>
       </c>
       <c r="M20" s="15">
-        <v>133.333333333333</v>
+        <v>96.296296296296</v>
       </c>
       <c r="N20" s="15">
-        <v>-73.513513513513</v>
+        <v>-75.348837209302</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,81 +1139,81 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D21" s="17">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="E21" s="18">
-        <v>2.631578947368</v>
+        <v>-24.074074074074</v>
       </c>
       <c r="F21" s="17">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G21" s="17">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.091954022988</v>
+        <v>-18.232044198895</v>
       </c>
       <c r="I21" s="17">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="J21" s="17">
-        <v>241</v>
+        <v>295</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.842323651452</v>
+        <v>-18.644067796610</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.255813953488</v>
+        <v>-19.191919191919</v>
       </c>
       <c r="M21" s="18">
-        <v>20.731707317073</v>
+        <v>27.659574468085</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.955752212389</v>
+        <v>-62.790697674418</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="13" t="s">
+      <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>22</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>3</v>
       </c>
       <c r="J22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="15">
+        <v>-25</v>
+      </c>
+      <c r="L22" s="15">
         <v>0</v>
-      </c>
-      <c r="L22" s="15">
-        <v>50</v>
       </c>
       <c r="M22" s="15">
         <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>33.333333333333</v>
+        <v>200</v>
       </c>
       <c r="F23" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
         <v>10</v>
       </c>
       <c r="H23" s="15">
+        <v>-10</v>
+      </c>
+      <c r="I23" s="14">
+        <v>16</v>
+      </c>
+      <c r="J23" s="14">
+        <v>16</v>
+      </c>
+      <c r="K23" s="15">
         <v>0</v>
       </c>
-      <c r="I23" s="14">
-        <v>13</v>
-      </c>
-      <c r="J23" s="14">
-        <v>15</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-13.333333333333</v>
-      </c>
       <c r="L23" s="15">
-        <v>-27.777777777777</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="M23" s="15">
-        <v>85.714285714285</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-20</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="G24" s="14">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H24" s="15">
-        <v>26.966292134831</v>
+        <v>-7.291666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="J24" s="14">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="K24" s="15">
-        <v>30.46875</v>
+        <v>24.342105263157</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.113636363636</v>
+        <v>-10.426540284360</v>
       </c>
       <c r="M24" s="15">
-        <v>43.965517241379</v>
+        <v>52.419354838709</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>-22.222222222222</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G25" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H25" s="15">
-        <v>51.612903225806</v>
+        <v>15.151515151515</v>
       </c>
       <c r="I25" s="14">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J25" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K25" s="15">
-        <v>42.857142857142</v>
+        <v>45.454545454545</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.647058823529</v>
+        <v>-24.528301886792</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-38.461538461538</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G26" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H26" s="15">
-        <v>-30</v>
+        <v>-26.415094339622</v>
       </c>
       <c r="I26" s="14">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="J26" s="14">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.9375</v>
+        <v>-15.189873417721</v>
       </c>
       <c r="L26" s="15">
-        <v>14</v>
+        <v>3.076923076923</v>
       </c>
       <c r="M26" s="15">
-        <v>1.785714285714</v>
+        <v>6.349206349206</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>22</v>
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>7</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="L27" s="15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1428,20 +1428,20 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
+        <v>8</v>
+      </c>
+      <c r="G28" s="14">
         <v>7</v>
       </c>
-      <c r="G28" s="14">
-        <v>10</v>
-      </c>
       <c r="H28" s="15">
-        <v>-30</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I28" s="14">
         <v>11</v>
@@ -1456,10 +1456,10 @@
         <v>57.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>2</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M29" s="15">
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,38 +1551,38 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="14">
-        <v>1</v>
-      </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="I31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H31" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" s="14">
-        <v>1</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>22</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>-100</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,16 +1614,16 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="14">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>34</v>

--- a/data/source/weekly/cs-en-us-049pct.xlsx
+++ b/data/source/weekly/cs-en-us-049pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
@@ -920,13 +920,13 @@
         <v>200</v>
       </c>
       <c r="L15" s="15">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="M15" s="15">
         <v>350</v>
       </c>
       <c r="N15" s="15">
-        <v>200</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-14.285714285714</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="I16" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J16" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K16" s="15">
-        <v>-5.263157894736</v>
+        <v>-2.380952380952</v>
       </c>
       <c r="L16" s="15">
-        <v>-7.692307692307</v>
+        <v>-4.651162790697</v>
       </c>
       <c r="M16" s="15">
-        <v>-23.404255319148</v>
+        <v>-12.765957446808</v>
       </c>
       <c r="N16" s="15">
-        <v>-69.747899159663</v>
+        <v>-67.96875</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G17" s="14">
         <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>3.448275862068</v>
       </c>
       <c r="I17" s="14">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J17" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K17" s="15">
-        <v>4</v>
+        <v>1.754385964912</v>
       </c>
       <c r="L17" s="15">
-        <v>0</v>
+        <v>5.454545454545</v>
       </c>
       <c r="M17" s="15">
-        <v>85.714285714285</v>
+        <v>65.714285714285</v>
       </c>
       <c r="N17" s="15">
-        <v>188.888888888889</v>
+        <v>163.636363636364</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
         <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
         <v>38</v>
       </c>
       <c r="H18" s="15">
-        <v>-63.157894736842</v>
+        <v>-55.263157894736</v>
       </c>
       <c r="I18" s="14">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J18" s="14">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K18" s="15">
-        <v>-56.521739130434</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="15">
-        <v>-9.090909090909</v>
+        <v>8</v>
       </c>
       <c r="M18" s="15">
-        <v>-50</v>
+        <v>-42.553191489361</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.909090909090</v>
+        <v>-89.370078740157</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="F19" s="14">
         <v>45</v>
       </c>
       <c r="G19" s="14">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H19" s="15">
-        <v>-15.094339622641</v>
+        <v>-32.835820895522</v>
       </c>
       <c r="I19" s="14">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J19" s="14">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="K19" s="15">
-        <v>-25.806451612903</v>
+        <v>-31.896551724137</v>
       </c>
       <c r="L19" s="15">
-        <v>-41.025641025641</v>
+        <v>-43.971631205673</v>
       </c>
       <c r="M19" s="15">
-        <v>60.465116279069</v>
+        <v>75.555555555555</v>
       </c>
       <c r="N19" s="15">
-        <v>4.545454545454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-63.636363636363</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F20" s="14">
+        <v>33</v>
+      </c>
+      <c r="G20" s="14">
         <v>36</v>
       </c>
-      <c r="G20" s="14">
-        <v>34</v>
-      </c>
       <c r="H20" s="15">
-        <v>5.882352941176</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J20" s="14">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="K20" s="15">
-        <v>-17.1875</v>
+        <v>-21.917808219178</v>
       </c>
       <c r="L20" s="15">
-        <v>-14.516129032258</v>
+        <v>-16.176470588235</v>
       </c>
       <c r="M20" s="15">
-        <v>96.296296296296</v>
+        <v>90</v>
       </c>
       <c r="N20" s="15">
-        <v>-75.348837209302</v>
+        <v>-77.2</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E21" s="18">
-        <v>-24.074074074074</v>
+        <v>-31.372549019607</v>
       </c>
       <c r="F21" s="17">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G21" s="17">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.232044198895</v>
+        <v>-24.615384615384</v>
       </c>
       <c r="I21" s="17">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="J21" s="17">
-        <v>295</v>
+        <v>346</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.644067796610</v>
+        <v>-21.387283236994</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.191919191919</v>
+        <v>-19.526627218934</v>
       </c>
       <c r="M21" s="18">
-        <v>27.659574468085</v>
+        <v>31.400966183574</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.790697674418</v>
+        <v>-63.292847503373</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
         <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1230,28 +1230,28 @@
         <v>200</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G23" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>-10</v>
+        <v>37.5</v>
       </c>
       <c r="I23" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J23" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>11.764705882352</v>
       </c>
       <c r="L23" s="15">
-        <v>-15.789473684210</v>
+        <v>-5</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14">
         <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-20.833333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G24" s="14">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H24" s="15">
-        <v>-7.291666666666</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="I24" s="14">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="J24" s="14">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="K24" s="15">
-        <v>24.342105263157</v>
+        <v>23.295454545454</v>
       </c>
       <c r="L24" s="15">
-        <v>-10.426540284360</v>
+        <v>-6.465517241379</v>
       </c>
       <c r="M24" s="15">
-        <v>52.419354838709</v>
+        <v>63.157894736842</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F25" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G25" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H25" s="15">
-        <v>15.151515151515</v>
+        <v>35.483870967741</v>
       </c>
       <c r="I25" s="14">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J25" s="14">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K25" s="15">
-        <v>45.454545454545</v>
+        <v>44.615384615384</v>
       </c>
       <c r="L25" s="15">
-        <v>-24.528301886792</v>
+        <v>-17.543859649122</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>-26.666666666666</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F26" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G26" s="14">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H26" s="15">
-        <v>-26.415094339622</v>
+        <v>-33.870967741935</v>
       </c>
       <c r="I26" s="14">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="J26" s="14">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="K26" s="15">
-        <v>-15.189873417721</v>
+        <v>-17.708333333333</v>
       </c>
       <c r="L26" s="15">
-        <v>3.076923076923</v>
+        <v>8.219178082191</v>
       </c>
       <c r="M26" s="15">
-        <v>6.349206349206</v>
+        <v>2.597402597402</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>250</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
         <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="L27" s="15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
         <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
         <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>57.142857142857</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1500,15 +1500,15 @@
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-049pct.xlsx
+++ b/data/source/weekly/cs-en-us-049pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L14" s="15">
         <v>0</v>
@@ -890,34 +890,34 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="L15" s="15">
         <v>80</v>
@@ -926,258 +926,258 @@
         <v>350</v>
       </c>
       <c r="N15" s="15">
-        <v>125</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G16" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H16" s="15">
-        <v>-22.727272727272</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I16" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J16" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K16" s="15">
-        <v>-2.380952380952</v>
+        <v>2.173913043478</v>
       </c>
       <c r="L16" s="15">
-        <v>-4.651162790697</v>
+        <v>-6</v>
       </c>
       <c r="M16" s="15">
-        <v>-12.765957446808</v>
+        <v>-11.320754716981</v>
       </c>
       <c r="N16" s="15">
-        <v>-67.96875</v>
+        <v>-66.428571428571</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
         <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G17" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H17" s="15">
-        <v>3.448275862068</v>
+        <v>18.75</v>
       </c>
       <c r="I17" s="14">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="J17" s="14">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="K17" s="15">
-        <v>1.754385964912</v>
+        <v>1.470588235294</v>
       </c>
       <c r="L17" s="15">
-        <v>5.454545454545</v>
+        <v>4.545454545454</v>
       </c>
       <c r="M17" s="15">
-        <v>65.714285714285</v>
+        <v>81.578947368421</v>
       </c>
       <c r="N17" s="15">
-        <v>163.636363636364</v>
+        <v>155.555555555556</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G18" s="14">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H18" s="15">
-        <v>-55.263157894736</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J18" s="14">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K18" s="15">
-        <v>-50</v>
+        <v>-46.551724137931</v>
       </c>
       <c r="L18" s="15">
-        <v>8</v>
+        <v>10.714285714285</v>
       </c>
       <c r="M18" s="15">
-        <v>-42.553191489361</v>
+        <v>-43.636363636363</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.370078740157</v>
+        <v>-89.045936395759</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-47.826086956521</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F19" s="14">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G19" s="14">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H19" s="15">
-        <v>-32.835820895522</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I19" s="14">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J19" s="14">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="K19" s="15">
-        <v>-31.896551724137</v>
+        <v>-31.782945736434</v>
       </c>
       <c r="L19" s="15">
-        <v>-43.971631205673</v>
+        <v>-48.235294117647</v>
       </c>
       <c r="M19" s="15">
-        <v>75.555555555555</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>0</v>
+        <v>3.529411764705</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E20" s="15">
-        <v>-55.555555555555</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="F20" s="14">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H20" s="15">
-        <v>-8.333333333333</v>
+        <v>-41.025641025641</v>
       </c>
       <c r="I20" s="14">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J20" s="14">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="K20" s="15">
-        <v>-21.917808219178</v>
+        <v>-30.232558139534</v>
       </c>
       <c r="L20" s="15">
-        <v>-16.176470588235</v>
+        <v>-24.050632911392</v>
       </c>
       <c r="M20" s="15">
-        <v>90</v>
+        <v>81.818181818181</v>
       </c>
       <c r="N20" s="15">
-        <v>-77.2</v>
+        <v>-79.094076655052</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E21" s="18">
-        <v>-31.372549019607</v>
+        <v>-31.25</v>
       </c>
       <c r="F21" s="17">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G21" s="17">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H21" s="18">
-        <v>-24.615384615384</v>
+        <v>-23.560209424083</v>
       </c>
       <c r="I21" s="17">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="J21" s="17">
-        <v>346</v>
+        <v>394</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.387283236994</v>
+        <v>-22.588832487309</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.526627218934</v>
+        <v>-23.558897243107</v>
       </c>
       <c r="M21" s="18">
-        <v>31.400966183574</v>
+        <v>32.608695652173</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.292847503373</v>
+        <v>-63.341346153846</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="14">
         <v>1</v>
@@ -1186,34 +1186,34 @@
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F22" s="14">
         <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>33.333333333333</v>
+        <v>300</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M22" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
         <v>3</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
       <c r="E23" s="15">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
         <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J23" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K23" s="15">
-        <v>11.764705882352</v>
+        <v>5</v>
       </c>
       <c r="L23" s="15">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="14">
         <v>90</v>
       </c>
       <c r="G24" s="14">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="H24" s="15">
-        <v>-3.225806451612</v>
+        <v>-12.621359223301</v>
       </c>
       <c r="I24" s="14">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="J24" s="14">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="K24" s="15">
-        <v>23.295454545454</v>
+        <v>15.048543689320</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.465517241379</v>
+        <v>-9.541984732824</v>
       </c>
       <c r="M24" s="15">
-        <v>63.157894736842</v>
+        <v>66.901408450704</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>40</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F25" s="14">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G25" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H25" s="15">
-        <v>35.483870967741</v>
+        <v>20.588235294117</v>
       </c>
       <c r="I25" s="14">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J25" s="14">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="K25" s="15">
-        <v>44.615384615384</v>
+        <v>40.540540540540</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.543859649122</v>
+        <v>-20</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1347,37 +1347,37 @@
         <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>-29.411764705882</v>
+        <v>20</v>
       </c>
       <c r="F26" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G26" s="14">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H26" s="15">
-        <v>-33.870967741935</v>
+        <v>-23.636363636363</v>
       </c>
       <c r="I26" s="14">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J26" s="14">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="K26" s="15">
-        <v>-17.708333333333</v>
+        <v>-14.150943396226</v>
       </c>
       <c r="L26" s="15">
-        <v>8.219178082191</v>
+        <v>13.75</v>
       </c>
       <c r="M26" s="15">
-        <v>2.597402597402</v>
+        <v>4.597701149425</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1388,37 +1388,37 @@
         <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
         <v>-100</v>
       </c>
       <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
         <v>4</v>
       </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="14">
         <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
         <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1435,113 +1435,113 @@
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
         <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>50</v>
+        <v>44.444444444444</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>2</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-50</v>
       </c>
       <c r="F29" s="14">
+        <v>4</v>
+      </c>
+      <c r="G29" s="14">
         <v>3</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
       <c r="H29" s="15">
-        <v>200</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I29" s="14">
+        <v>4</v>
+      </c>
+      <c r="J29" s="14">
         <v>3</v>
       </c>
-      <c r="J29" s="14">
-        <v>1</v>
-      </c>
       <c r="K29" s="15">
-        <v>200</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>200</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
+        <v>3</v>
+      </c>
+      <c r="G30" s="14">
         <v>2</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I30" s="14">
+        <v>3</v>
+      </c>
+      <c r="J30" s="14">
         <v>2</v>
       </c>
-      <c r="J30" s="14">
-        <v>1</v>
-      </c>
       <c r="K30" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1576,13 +1576,13 @@
         <v>-100</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>34</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>766</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>363</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>1439</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>686</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>2991</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>6295</v>

--- a/data/source/weekly/cs-en-us-049pct.xlsx
+++ b/data/source/weekly/cs-en-us-049pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,20 +854,20 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -890,312 +890,312 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
-      </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>80</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>80</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
+        <v>25</v>
+      </c>
+      <c r="F16" s="14">
+        <v>22</v>
+      </c>
+      <c r="G16" s="14">
+        <v>19</v>
+      </c>
+      <c r="H16" s="15">
+        <v>15.789473684210</v>
+      </c>
+      <c r="I16" s="14">
+        <v>52</v>
+      </c>
+      <c r="J16" s="14">
         <v>50</v>
       </c>
-      <c r="F16" s="14">
-        <v>19</v>
-      </c>
-      <c r="G16" s="14">
-        <v>21</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-9.523809523809</v>
-      </c>
-      <c r="I16" s="14">
-        <v>47</v>
-      </c>
-      <c r="J16" s="14">
-        <v>46</v>
-      </c>
       <c r="K16" s="15">
-        <v>2.173913043478</v>
+        <v>4</v>
       </c>
       <c r="L16" s="15">
-        <v>-6</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="M16" s="15">
-        <v>-11.320754716981</v>
+        <v>-14.754098360655</v>
       </c>
       <c r="N16" s="15">
-        <v>-66.428571428571</v>
+        <v>-66.013071895424</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G17" s="14">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H17" s="15">
-        <v>18.75</v>
+        <v>10.714285714285</v>
       </c>
       <c r="I17" s="14">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J17" s="14">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K17" s="15">
-        <v>1.470588235294</v>
+        <v>2.777777777777</v>
       </c>
       <c r="L17" s="15">
-        <v>4.545454545454</v>
+        <v>-9.756097560975</v>
       </c>
       <c r="M17" s="15">
-        <v>81.578947368421</v>
+        <v>80.487804878048</v>
       </c>
       <c r="N17" s="15">
-        <v>155.555555555556</v>
+        <v>146.666666666667</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
         <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
+        <v>-20</v>
+      </c>
+      <c r="F18" s="14">
+        <v>21</v>
+      </c>
+      <c r="G18" s="14">
+        <v>25</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-16</v>
+      </c>
+      <c r="I18" s="14">
+        <v>35</v>
+      </c>
+      <c r="J18" s="14">
+        <v>63</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-44.444444444444</v>
+      </c>
+      <c r="L18" s="15">
         <v>0</v>
       </c>
-      <c r="F18" s="14">
-        <v>20</v>
-      </c>
-      <c r="G18" s="14">
-        <v>28</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-28.571428571428</v>
-      </c>
-      <c r="I18" s="14">
-        <v>31</v>
-      </c>
-      <c r="J18" s="14">
-        <v>58</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-46.551724137931</v>
-      </c>
-      <c r="L18" s="15">
-        <v>10.714285714285</v>
-      </c>
       <c r="M18" s="15">
-        <v>-43.636363636363</v>
+        <v>-42.622950819672</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.045936395759</v>
+        <v>-88.372093023255</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14">
         <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-30.769230769230</v>
+        <v>38.461538461538</v>
       </c>
       <c r="F19" s="14">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G19" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H19" s="15">
-        <v>-36.363636363636</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="I19" s="14">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="J19" s="14">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="K19" s="15">
-        <v>-31.782945736434</v>
+        <v>-25.352112676056</v>
       </c>
       <c r="L19" s="15">
-        <v>-48.235294117647</v>
+        <v>-43.617021276595</v>
       </c>
       <c r="M19" s="15">
-        <v>83.333333333333</v>
+        <v>107.843137254902</v>
       </c>
       <c r="N19" s="15">
-        <v>3.529411764705</v>
+        <v>15.217391304347</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E20" s="15">
-        <v>-76.923076923076</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F20" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G20" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H20" s="15">
-        <v>-41.025641025641</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="I20" s="14">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J20" s="14">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K20" s="15">
-        <v>-30.232558139534</v>
+        <v>-30.927835051546</v>
       </c>
       <c r="L20" s="15">
-        <v>-24.050632911392</v>
+        <v>-25.555555555555</v>
       </c>
       <c r="M20" s="15">
-        <v>81.818181818181</v>
+        <v>86.111111111111</v>
       </c>
       <c r="N20" s="15">
-        <v>-79.094076655052</v>
+        <v>-79.635258358662</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D21" s="17">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E21" s="18">
-        <v>-31.25</v>
+        <v>7.894736842105</v>
       </c>
       <c r="F21" s="17">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G21" s="17">
         <v>191</v>
       </c>
       <c r="H21" s="18">
-        <v>-23.560209424083</v>
+        <v>-23.036649214659</v>
       </c>
       <c r="I21" s="17">
-        <v>305</v>
+        <v>345</v>
       </c>
       <c r="J21" s="17">
-        <v>394</v>
+        <v>432</v>
       </c>
       <c r="K21" s="18">
-        <v>-22.588832487309</v>
+        <v>-20.138888888888</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.558897243107</v>
+        <v>-24.342105263157</v>
       </c>
       <c r="M21" s="18">
-        <v>32.608695652173</v>
+        <v>36.363636363636</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.341346153846</v>
+        <v>-62.295081967213</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="14">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
         <v>5</v>
@@ -1207,13 +1207,13 @@
         <v>25</v>
       </c>
       <c r="L22" s="15">
+        <v>0</v>
+      </c>
+      <c r="M22" s="15">
         <v>25</v>
       </c>
-      <c r="M22" s="15">
-        <v>66.666666666666</v>
-      </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1223,38 +1223,38 @@
       <c r="C23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="14">
-        <v>3</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-33.333333333333</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I23" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J23" s="14">
         <v>20</v>
       </c>
       <c r="K23" s="15">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>110</v>
+        <v>109.090909090909</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>-33.333333333333</v>
+        <v>39.130434782608</v>
       </c>
       <c r="F24" s="14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G24" s="14">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H24" s="15">
-        <v>-12.621359223301</v>
+        <v>-0.990099009900</v>
       </c>
       <c r="I24" s="14">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="J24" s="14">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="K24" s="15">
-        <v>15.048543689320</v>
+        <v>17.903930131004</v>
       </c>
       <c r="L24" s="15">
-        <v>-9.541984732824</v>
+        <v>-8.163265306122</v>
       </c>
       <c r="M24" s="15">
-        <v>66.901408450704</v>
+        <v>77.631578947368</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>11.111111111111</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F25" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G25" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H25" s="15">
-        <v>20.588235294117</v>
+        <v>31.25</v>
       </c>
       <c r="I25" s="14">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="J25" s="14">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="K25" s="15">
-        <v>40.540540540540</v>
+        <v>39.506172839506</v>
       </c>
       <c r="L25" s="15">
-        <v>-20</v>
+        <v>-18.705035971223</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,81 +1344,81 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>20</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F26" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G26" s="14">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H26" s="15">
-        <v>-23.636363636363</v>
+        <v>-7.843137254901</v>
       </c>
       <c r="I26" s="14">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="J26" s="14">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="K26" s="15">
-        <v>-14.150943396226</v>
+        <v>-10.434782608695</v>
       </c>
       <c r="L26" s="15">
-        <v>13.75</v>
+        <v>11.956521739130</v>
       </c>
       <c r="M26" s="15">
-        <v>4.597701149425</v>
+        <v>0</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>-25</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,63 +1426,63 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>33.333333333333</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J28" s="14">
         <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L28" s="15">
-        <v>44.444444444444</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
         <v>2</v>
       </c>
-      <c r="E29" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F29" s="14">
-        <v>4</v>
-      </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>4</v>
@@ -1507,23 +1507,23 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
+        <v>2</v>
+      </c>
+      <c r="G30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
-      </c>
-      <c r="F30" s="14">
-        <v>3</v>
-      </c>
-      <c r="G30" s="14">
-        <v>2</v>
-      </c>
       <c r="H30" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1576,13 +1576,13 @@
         <v>-100</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>34</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>766</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>363</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>1439</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>686</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>2991</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>6295</v>

--- a/data/source/weekly/cs-en-us-049pct.xlsx
+++ b/data/source/weekly/cs-en-us-049pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -860,14 +860,14 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -892,38 +892,38 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2</v>
-      </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
         <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>66.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L15" s="15">
         <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>400</v>
+        <v>233.333333333333</v>
       </c>
       <c r="N15" s="15">
         <v>66.666666666666</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G16" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>15.789473684210</v>
+        <v>35.714285714285</v>
       </c>
       <c r="I16" s="14">
+        <v>55</v>
+      </c>
+      <c r="J16" s="14">
         <v>52</v>
       </c>
-      <c r="J16" s="14">
-        <v>50</v>
-      </c>
       <c r="K16" s="15">
-        <v>4</v>
+        <v>5.769230769230</v>
       </c>
       <c r="L16" s="15">
-        <v>-3.703703703703</v>
+        <v>-3.508771929824</v>
       </c>
       <c r="M16" s="15">
-        <v>-14.754098360655</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-66.013071895424</v>
+        <v>-66.257668711656</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
         <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G17" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H17" s="15">
-        <v>10.714285714285</v>
+        <v>28.125</v>
       </c>
       <c r="I17" s="14">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="J17" s="14">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="K17" s="15">
-        <v>2.777777777777</v>
+        <v>10.975609756097</v>
       </c>
       <c r="L17" s="15">
-        <v>-9.756097560975</v>
+        <v>4.597701149425</v>
       </c>
       <c r="M17" s="15">
-        <v>80.487804878048</v>
+        <v>78.431372549019</v>
       </c>
       <c r="N17" s="15">
-        <v>146.666666666667</v>
+        <v>139.473684210526</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>-20</v>
       </c>
       <c r="F18" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G18" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H18" s="15">
-        <v>-16</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I18" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J18" s="14">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K18" s="15">
-        <v>-44.444444444444</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="L18" s="15">
-        <v>0</v>
+        <v>2.564102564102</v>
       </c>
       <c r="M18" s="15">
-        <v>-42.622950819672</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.372093023255</v>
+        <v>-87.692307692307</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>38.461538461538</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G19" s="14">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="H19" s="15">
-        <v>-25.714285714285</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I19" s="14">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="J19" s="14">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="K19" s="15">
-        <v>-25.352112676056</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L19" s="15">
-        <v>-43.617021276595</v>
+        <v>-42.583732057416</v>
       </c>
       <c r="M19" s="15">
-        <v>107.843137254902</v>
+        <v>118.181818181818</v>
       </c>
       <c r="N19" s="15">
-        <v>15.217391304347</v>
+        <v>17.647058823529</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>-36.363636363636</v>
       </c>
       <c r="F20" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
         <v>44</v>
       </c>
       <c r="H20" s="15">
-        <v>-59.090909090909</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I20" s="14">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J20" s="14">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="K20" s="15">
-        <v>-30.927835051546</v>
+        <v>-32.407407407407</v>
       </c>
       <c r="L20" s="15">
-        <v>-25.555555555555</v>
+        <v>-26.262626262626</v>
       </c>
       <c r="M20" s="15">
-        <v>86.111111111111</v>
+        <v>97.297297297297</v>
       </c>
       <c r="N20" s="15">
-        <v>-79.635258358662</v>
+        <v>-79.494382022471</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D21" s="17">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E21" s="18">
-        <v>7.894736842105</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G21" s="17">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="H21" s="18">
-        <v>-23.036649214659</v>
+        <v>-13.407821229050</v>
       </c>
       <c r="I21" s="17">
-        <v>345</v>
+        <v>390</v>
       </c>
       <c r="J21" s="17">
-        <v>432</v>
+        <v>475</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.138888888888</v>
+        <v>-17.894736842105</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.342105263157</v>
+        <v>-21.686746987951</v>
       </c>
       <c r="M21" s="18">
-        <v>36.363636363636</v>
+        <v>40.287769784172</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.295081967213</v>
+        <v>-60.764587525150</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
-      </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M22" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J23" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K23" s="15">
-        <v>15</v>
+        <v>13.636363636363</v>
       </c>
       <c r="L23" s="15">
-        <v>-4.166666666666</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="M23" s="15">
-        <v>109.090909090909</v>
+        <v>92.307692307692</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>39.130434782608</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="F24" s="14">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G24" s="14">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H24" s="15">
-        <v>-0.990099009900</v>
+        <v>-3.603603603603</v>
       </c>
       <c r="I24" s="14">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="J24" s="14">
-        <v>229</v>
+        <v>263</v>
       </c>
       <c r="K24" s="15">
-        <v>17.903930131004</v>
+        <v>12.547528517110</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.163265306122</v>
+        <v>-10.574018126888</v>
       </c>
       <c r="M24" s="15">
-        <v>77.631578947368</v>
+        <v>77.245508982035</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G25" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H25" s="15">
-        <v>31.25</v>
+        <v>19.444444444444</v>
       </c>
       <c r="I25" s="14">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="J25" s="14">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K25" s="15">
-        <v>39.506172839506</v>
+        <v>35.164835164835</v>
       </c>
       <c r="L25" s="15">
-        <v>-18.705035971223</v>
+        <v>-19.607843137254</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>55.555555555555</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="F26" s="14">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G26" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H26" s="15">
-        <v>-7.843137254901</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I26" s="14">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="J26" s="14">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.434782608695</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L26" s="15">
-        <v>11.956521739130</v>
+        <v>9.615384615384</v>
       </c>
       <c r="M26" s="15">
-        <v>0</v>
+        <v>0.884955752212</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F27" s="14">
-        <v>2</v>
-      </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L27" s="15">
         <v>42.857142857142</v>
@@ -1426,22 +1426,22 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
         <v>3</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="14">
-        <v>6</v>
-      </c>
-      <c r="G28" s="14">
-        <v>2</v>
-      </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="14">
         <v>16</v>
@@ -1453,7 +1453,7 @@
         <v>23.076923076923</v>
       </c>
       <c r="L28" s="15">
-        <v>33.333333333333</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,13 +1476,13 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>4</v>
@@ -1497,10 +1497,10 @@
         <v>33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-20</v>
+        <v>-42.857142857142</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,13 +1517,13 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
@@ -1538,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="N30" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1634,8 +1634,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-049pct.xlsx
+++ b/data/source/weekly/cs-en-us-049pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" s="14">
         <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>42.857142857142</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L15" s="15">
-        <v>66.666666666666</v>
+        <v>10</v>
       </c>
       <c r="M15" s="15">
-        <v>233.333333333333</v>
+        <v>175</v>
       </c>
       <c r="N15" s="15">
-        <v>66.666666666666</v>
+        <v>83.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>35.714285714285</v>
+        <v>73.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="J16" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K16" s="15">
-        <v>5.769230769230</v>
+        <v>17.543859649122</v>
       </c>
       <c r="L16" s="15">
-        <v>-3.508771929824</v>
+        <v>8.064516129032</v>
       </c>
       <c r="M16" s="15">
-        <v>-16.666666666666</v>
+        <v>-6.944444444444</v>
       </c>
       <c r="N16" s="15">
-        <v>-66.257668711656</v>
+        <v>-62.777777777777</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F17" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G17" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H17" s="15">
-        <v>28.125</v>
+        <v>21.052631578947</v>
       </c>
       <c r="I17" s="14">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="J17" s="14">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K17" s="15">
-        <v>10.975609756097</v>
+        <v>8.421052631578</v>
       </c>
       <c r="L17" s="15">
-        <v>4.597701149425</v>
+        <v>7.291666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>78.431372549019</v>
+        <v>80.701754385964</v>
       </c>
       <c r="N17" s="15">
-        <v>139.473684210526</v>
+        <v>123.913043478261</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-20</v>
+        <v>150</v>
       </c>
       <c r="F18" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-9.090909090909</v>
+        <v>12.5</v>
       </c>
       <c r="I18" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J18" s="14">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K18" s="15">
-        <v>-41.176470588235</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L18" s="15">
-        <v>2.564102564102</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M18" s="15">
-        <v>-38.461538461538</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.692307692307</v>
+        <v>-87.465181058495</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>58</v>
+      </c>
+      <c r="G19" s="14">
+        <v>55</v>
+      </c>
+      <c r="H19" s="15">
+        <v>5.454545454545</v>
+      </c>
+      <c r="I19" s="14">
+        <v>136</v>
+      </c>
+      <c r="J19" s="14">
+        <v>171</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-20.467836257309</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-40.869565217391</v>
+      </c>
+      <c r="M19" s="15">
+        <v>106.060606060606</v>
+      </c>
+      <c r="N19" s="15">
         <v>14.285714285714</v>
-      </c>
-      <c r="F19" s="14">
-        <v>54</v>
-      </c>
-      <c r="G19" s="14">
-        <v>63</v>
-      </c>
-      <c r="H19" s="15">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="I19" s="14">
-        <v>120</v>
-      </c>
-      <c r="J19" s="14">
-        <v>156</v>
-      </c>
-      <c r="K19" s="15">
-        <v>-23.076923076923</v>
-      </c>
-      <c r="L19" s="15">
-        <v>-42.583732057416</v>
-      </c>
-      <c r="M19" s="15">
-        <v>118.181818181818</v>
-      </c>
-      <c r="N19" s="15">
-        <v>17.647058823529</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-36.363636363636</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
         <v>20</v>
       </c>
       <c r="G20" s="14">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H20" s="15">
-        <v>-54.545454545454</v>
+        <v>-51.219512195122</v>
       </c>
       <c r="I20" s="14">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J20" s="14">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="K20" s="15">
-        <v>-32.407407407407</v>
+        <v>-32.456140350877</v>
       </c>
       <c r="L20" s="15">
-        <v>-26.262626262626</v>
+        <v>-29.357798165137</v>
       </c>
       <c r="M20" s="15">
-        <v>97.297297297297</v>
+        <v>87.804878048780</v>
       </c>
       <c r="N20" s="15">
-        <v>-79.494382022471</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D21" s="17">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>7.142857142857</v>
+        <v>17.073170731707</v>
       </c>
       <c r="F21" s="17">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="G21" s="17">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.407821229050</v>
+        <v>0.591715976331</v>
       </c>
       <c r="I21" s="17">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="J21" s="17">
-        <v>475</v>
+        <v>516</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.894736842105</v>
+        <v>-14.728682170542</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.686746987951</v>
+        <v>-20</v>
       </c>
       <c r="M21" s="18">
-        <v>40.287769784172</v>
+        <v>41.479099678456</v>
       </c>
       <c r="N21" s="18">
-        <v>-60.764587525150</v>
+        <v>-59.963603275705</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L22" s="15">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M22" s="15">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
         <v>0</v>
       </c>
       <c r="F23" s="14">
+        <v>10</v>
+      </c>
+      <c r="G23" s="14">
         <v>9</v>
       </c>
-      <c r="G23" s="14">
-        <v>6</v>
-      </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I23" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J23" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K23" s="15">
-        <v>13.636363636363</v>
+        <v>11.538461538461</v>
       </c>
       <c r="L23" s="15">
-        <v>-7.407407407407</v>
+        <v>3.571428571428</v>
       </c>
       <c r="M23" s="15">
-        <v>92.307692307692</v>
+        <v>81.25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-23.529411764705</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F24" s="14">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G24" s="14">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H24" s="15">
-        <v>-3.603603603603</v>
+        <v>-12.173913043478</v>
       </c>
       <c r="I24" s="14">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="J24" s="14">
-        <v>263</v>
+        <v>291</v>
       </c>
       <c r="K24" s="15">
-        <v>12.547528517110</v>
+        <v>9.278350515463</v>
       </c>
       <c r="L24" s="15">
-        <v>-10.574018126888</v>
+        <v>-13.351498637602</v>
       </c>
       <c r="M24" s="15">
-        <v>77.245508982035</v>
+        <v>74.725274725274</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
         <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G25" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H25" s="15">
-        <v>19.444444444444</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I25" s="14">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="J25" s="14">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="K25" s="15">
-        <v>35.164835164835</v>
+        <v>30.769230769230</v>
       </c>
       <c r="L25" s="15">
-        <v>-19.607843137254</v>
+        <v>-20.467836257309</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-38.888888888888</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F26" s="14">
         <v>48</v>
       </c>
       <c r="G26" s="14">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H26" s="15">
-        <v>-11.111111111111</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="I26" s="14">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="J26" s="14">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="K26" s="15">
-        <v>-14.285714285714</v>
+        <v>-13.103448275862</v>
       </c>
       <c r="L26" s="15">
-        <v>9.615384615384</v>
+        <v>7.692307692307</v>
       </c>
       <c r="M26" s="15">
-        <v>0.884955752212</v>
+        <v>-5.970149253731</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-80</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>11.111111111111</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L27" s="15">
-        <v>42.857142857142</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>66.666666666666</v>
+        <v>75</v>
       </c>
       <c r="I28" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>23.076923076923</v>
+        <v>26.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>23.076923076923</v>
+        <v>35.714285714285</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-42.857142857142</v>
+        <v>-63.636363636363</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-25</v>
       </c>
       <c r="N30" s="15">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-049pct.xlsx
+++ b/data/source/weekly/cs-en-us-049pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
         <v>-75</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>300</v>
       </c>
       <c r="I15" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J15" s="14">
         <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>57.142857142857</v>
+        <v>85.714285714285</v>
       </c>
       <c r="L15" s="15">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M15" s="15">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="N15" s="15">
-        <v>83.333333333333</v>
+        <v>116.666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>73.333333333333</v>
+        <v>92.857142857142</v>
       </c>
       <c r="I16" s="14">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="J16" s="14">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K16" s="15">
-        <v>17.543859649122</v>
+        <v>23.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>8.064516129032</v>
+        <v>7.246376811594</v>
       </c>
       <c r="M16" s="15">
-        <v>-6.944444444444</v>
+        <v>-1.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-62.777777777777</v>
+        <v>-61.855670103092</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-7.692307692307</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G17" s="14">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H17" s="15">
-        <v>21.052631578947</v>
+        <v>36.363636363636</v>
       </c>
       <c r="I17" s="14">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="J17" s="14">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="K17" s="15">
-        <v>8.421052631578</v>
+        <v>11.881188118811</v>
       </c>
       <c r="L17" s="15">
-        <v>7.291666666666</v>
+        <v>8.653846153846</v>
       </c>
       <c r="M17" s="15">
-        <v>80.701754385964</v>
+        <v>79.365079365079</v>
       </c>
       <c r="N17" s="15">
-        <v>123.913043478261</v>
+        <v>109.259259259259</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>150</v>
+        <v>-25</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
         <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="I18" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J18" s="14">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K18" s="15">
-        <v>-35.714285714285</v>
+        <v>-35.135135135135</v>
       </c>
       <c r="L18" s="15">
-        <v>7.142857142857</v>
+        <v>4.347826086956</v>
       </c>
       <c r="M18" s="15">
-        <v>-35.714285714285</v>
+        <v>-37.662337662337</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.465181058495</v>
+        <v>-87.939698492462</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F19" s="14">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G19" s="14">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H19" s="15">
-        <v>5.454545454545</v>
+        <v>3.278688524590</v>
       </c>
       <c r="I19" s="14">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="J19" s="14">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="K19" s="15">
-        <v>-20.467836257309</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="L19" s="15">
-        <v>-40.869565217391</v>
+        <v>-39.271255060728</v>
       </c>
       <c r="M19" s="15">
-        <v>106.060606060606</v>
+        <v>114.285714285714</v>
       </c>
       <c r="N19" s="15">
-        <v>14.285714285714</v>
+        <v>12.781954887218</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F20" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G20" s="14">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H20" s="15">
-        <v>-51.219512195122</v>
+        <v>-43.243243243243</v>
       </c>
       <c r="I20" s="14">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J20" s="14">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="K20" s="15">
-        <v>-32.456140350877</v>
+        <v>-34.146341463414</v>
       </c>
       <c r="L20" s="15">
-        <v>-29.357798165137</v>
+        <v>-28.318584070796</v>
       </c>
       <c r="M20" s="15">
-        <v>87.804878048780</v>
+        <v>65.306122448979</v>
       </c>
       <c r="N20" s="15">
-        <v>-80</v>
+        <v>-81.074766355140</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D21" s="17">
         <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>17.073170731707</v>
+        <v>-4.878048780487</v>
       </c>
       <c r="F21" s="17">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="G21" s="17">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="H21" s="18">
-        <v>0.591715976331</v>
+        <v>9.259259259259</v>
       </c>
       <c r="I21" s="17">
-        <v>440</v>
+        <v>480</v>
       </c>
       <c r="J21" s="17">
-        <v>516</v>
+        <v>557</v>
       </c>
       <c r="K21" s="18">
-        <v>-14.728682170542</v>
+        <v>-13.824057450628</v>
       </c>
       <c r="L21" s="18">
-        <v>-20</v>
+        <v>-18.644067796610</v>
       </c>
       <c r="M21" s="18">
-        <v>41.479099678456</v>
+        <v>41.176470588235</v>
       </c>
       <c r="N21" s="18">
-        <v>-59.963603275705</v>
+        <v>-60.558751027115</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
       </c>
       <c r="F22" s="14">
         <v>4</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>300</v>
       </c>
       <c r="I22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L22" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G23" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>11.111111111111</v>
+        <v>62.5</v>
       </c>
       <c r="I23" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J23" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K23" s="15">
-        <v>11.538461538461</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L23" s="15">
-        <v>3.571428571428</v>
+        <v>17.241379310344</v>
       </c>
       <c r="M23" s="15">
-        <v>81.25</v>
+        <v>88.888888888888</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E24" s="15">
-        <v>-14.285714285714</v>
+        <v>13.513513513513</v>
       </c>
       <c r="F24" s="14">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="G24" s="14">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H24" s="15">
-        <v>-12.173913043478</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>318</v>
+        <v>360</v>
       </c>
       <c r="J24" s="14">
-        <v>291</v>
+        <v>328</v>
       </c>
       <c r="K24" s="15">
-        <v>9.278350515463</v>
+        <v>9.756097560975</v>
       </c>
       <c r="L24" s="15">
-        <v>-13.351498637602</v>
+        <v>-7.455012853470</v>
       </c>
       <c r="M24" s="15">
-        <v>74.725274725274</v>
+        <v>77.339901477832</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>77.777777777777</v>
       </c>
       <c r="F25" s="14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G25" s="14">
         <v>39</v>
       </c>
       <c r="H25" s="15">
-        <v>7.692307692307</v>
+        <v>23.076923076923</v>
       </c>
       <c r="I25" s="14">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="J25" s="14">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K25" s="15">
-        <v>30.769230769230</v>
+        <v>34.513274336283</v>
       </c>
       <c r="L25" s="15">
-        <v>-20.467836257309</v>
+        <v>-16.939890710382</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>-8.333333333333</v>
+        <v>533.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G26" s="14">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>-2.040816326530</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="J26" s="14">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K26" s="15">
-        <v>-13.103448275862</v>
+        <v>-2.027027027027</v>
       </c>
       <c r="L26" s="15">
-        <v>7.692307692307</v>
+        <v>13.28125</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.970149253731</v>
+        <v>0</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
+        <v>4</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="14">
-        <v>4</v>
-      </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>22.222222222222</v>
+        <v>44.444444444444</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1438,22 +1438,22 @@
         <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>26.666666666666</v>
+        <v>17.647058823529</v>
       </c>
       <c r="L28" s="15">
-        <v>35.714285714285</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,14 +1475,14 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
-      </c>
-      <c r="G29" s="14">
-        <v>2</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-50</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>4</v>
@@ -1497,7 +1497,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
         <v>-63.636363636363</v>
@@ -1516,14 +1516,14 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
-      </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>0</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
         <v>-62.5</v>

--- a/data/source/weekly/cs-en-us-049pct.xlsx
+++ b/data/source/weekly/cs-en-us-049pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>300</v>
+        <v>3</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" s="14">
         <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>85.714285714285</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>30</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M15" s="15">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="N15" s="15">
-        <v>116.666666666667</v>
+        <v>133.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F16" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G16" s="14">
         <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>92.857142857142</v>
+        <v>121.428571428571</v>
       </c>
       <c r="I16" s="14">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J16" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K16" s="15">
-        <v>23.333333333333</v>
+        <v>31.25</v>
       </c>
       <c r="L16" s="15">
-        <v>7.246376811594</v>
+        <v>15.068493150684</v>
       </c>
       <c r="M16" s="15">
-        <v>-1.333333333333</v>
+        <v>9.090909090909</v>
       </c>
       <c r="N16" s="15">
-        <v>-61.855670103092</v>
+        <v>-58</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>66.666666666666</v>
+        <v>88.888888888888</v>
       </c>
       <c r="F17" s="14">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="G17" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H17" s="15">
-        <v>36.363636363636</v>
+        <v>47.368421052631</v>
       </c>
       <c r="I17" s="14">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="J17" s="14">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="K17" s="15">
-        <v>11.881188118811</v>
+        <v>20</v>
       </c>
       <c r="L17" s="15">
-        <v>8.653846153846</v>
+        <v>18.918918918918</v>
       </c>
       <c r="M17" s="15">
-        <v>79.365079365079</v>
+        <v>97.014925373134</v>
       </c>
       <c r="N17" s="15">
-        <v>109.259259259259</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>-25</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>6.25</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="I18" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J18" s="14">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K18" s="15">
-        <v>-35.135135135135</v>
+        <v>-39.024390243902</v>
       </c>
       <c r="L18" s="15">
-        <v>4.347826086956</v>
+        <v>2.040816326530</v>
       </c>
       <c r="M18" s="15">
-        <v>-37.662337662337</v>
+        <v>-38.271604938271</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.939698492462</v>
+        <v>-88.372093023255</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-21.052631578947</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F19" s="14">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G19" s="14">
         <v>61</v>
       </c>
       <c r="H19" s="15">
-        <v>3.278688524590</v>
+        <v>-4.918032786885</v>
       </c>
       <c r="I19" s="14">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="J19" s="14">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="K19" s="15">
-        <v>-21.052631578947</v>
+        <v>-20.197044334975</v>
       </c>
       <c r="L19" s="15">
-        <v>-39.271255060728</v>
+        <v>-38.167938931297</v>
       </c>
       <c r="M19" s="15">
-        <v>114.285714285714</v>
+        <v>105.063291139241</v>
       </c>
       <c r="N19" s="15">
-        <v>12.781954887218</v>
+        <v>14.893617021276</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>-55.555555555555</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H20" s="15">
-        <v>-43.243243243243</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="I20" s="14">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J20" s="14">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="K20" s="15">
-        <v>-34.146341463414</v>
+        <v>-32.061068702290</v>
       </c>
       <c r="L20" s="15">
-        <v>-28.318584070796</v>
+        <v>-27.642276422764</v>
       </c>
       <c r="M20" s="15">
-        <v>65.306122448979</v>
+        <v>50.847457627118</v>
       </c>
       <c r="N20" s="15">
-        <v>-81.074766355140</v>
+        <v>-80.044843049327</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E21" s="18">
-        <v>-4.878048780487</v>
+        <v>19.047619047619</v>
       </c>
       <c r="F21" s="17">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="G21" s="17">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H21" s="18">
-        <v>9.259259259259</v>
+        <v>11.445783132530</v>
       </c>
       <c r="I21" s="17">
-        <v>480</v>
+        <v>532</v>
       </c>
       <c r="J21" s="17">
-        <v>557</v>
+        <v>599</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.824057450628</v>
+        <v>-11.185308848080</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.644067796610</v>
+        <v>-15.555555555555</v>
       </c>
       <c r="M21" s="18">
-        <v>41.176470588235</v>
+        <v>43.783783783783</v>
       </c>
       <c r="N21" s="18">
-        <v>-60.558751027115</v>
+        <v>-58.855375096674</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>4</v>
@@ -1207,7 +1207,7 @@
         <v>80</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M22" s="15">
         <v>50</v>
@@ -1230,28 +1230,28 @@
         <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J23" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K23" s="15">
-        <v>21.428571428571</v>
+        <v>30</v>
       </c>
       <c r="L23" s="15">
-        <v>17.241379310344</v>
+        <v>25.806451612903</v>
       </c>
       <c r="M23" s="15">
-        <v>88.888888888888</v>
+        <v>116.666666666667</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>13.513513513513</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="F24" s="14">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="G24" s="14">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>-10.317460317460</v>
       </c>
       <c r="I24" s="14">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="J24" s="14">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="K24" s="15">
-        <v>9.756097560975</v>
+        <v>7.605633802816</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.455012853470</v>
+        <v>-8.612440191387</v>
       </c>
       <c r="M24" s="15">
-        <v>77.339901477832</v>
+        <v>71.300448430493</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
         <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>77.777777777777</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F25" s="14">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G25" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H25" s="15">
-        <v>23.076923076923</v>
+        <v>14.634146341463</v>
       </c>
       <c r="I25" s="14">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="J25" s="14">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="K25" s="15">
-        <v>34.513274336283</v>
+        <v>31.147540983606</v>
       </c>
       <c r="L25" s="15">
-        <v>-16.939890710382</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>18</v>
+      </c>
+      <c r="D26" s="14">
         <v>19</v>
       </c>
-      <c r="D26" s="14">
-        <v>3</v>
-      </c>
       <c r="E26" s="15">
-        <v>533.333333333333</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="F26" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G26" s="14">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H26" s="15">
-        <v>33.333333333333</v>
+        <v>13.461538461538</v>
       </c>
       <c r="I26" s="14">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="J26" s="14">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.027027027027</v>
+        <v>-2.994011976047</v>
       </c>
       <c r="L26" s="15">
-        <v>13.28125</v>
+        <v>21.804511278195</v>
       </c>
       <c r="M26" s="15">
-        <v>0</v>
+        <v>2.531645569620</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
-      </c>
-      <c r="G27" s="14">
-        <v>2</v>
-      </c>
-      <c r="H27" s="15">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>44.444444444444</v>
+        <v>55.555555555555</v>
       </c>
       <c r="L27" s="15">
-        <v>18.181818181818</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
+        <v>6</v>
+      </c>
+      <c r="G28" s="14">
         <v>7</v>
       </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
       <c r="H28" s="15">
-        <v>40</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I28" s="14">
         <v>20</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>17.647058823529</v>
+        <v>5.263157894736</v>
       </c>
       <c r="L28" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="14">
         <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-63.636363636363</v>
+        <v>-54.545454545454</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M30" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="N30" s="15">
         <v>-50</v>
-      </c>
-      <c r="N30" s="15">
-        <v>-62.5</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-049pct.xlsx
+++ b/data/source/weekly/cs-en-us-049pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" s="14">
         <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>114.285714285714</v>
       </c>
       <c r="L15" s="15">
-        <v>27.272727272727</v>
+        <v>15.384615384615</v>
       </c>
       <c r="M15" s="15">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>133.333333333333</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>150</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H16" s="15">
-        <v>121.428571428571</v>
+        <v>88.888888888888</v>
       </c>
       <c r="I16" s="14">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="J16" s="14">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K16" s="15">
-        <v>31.25</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L16" s="15">
-        <v>15.068493150684</v>
+        <v>13.924050632911</v>
       </c>
       <c r="M16" s="15">
-        <v>9.090909090909</v>
+        <v>12.5</v>
       </c>
       <c r="N16" s="15">
-        <v>-58</v>
+        <v>-57.746478873239</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>88.888888888888</v>
+        <v>300</v>
       </c>
       <c r="F17" s="14">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G17" s="14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H17" s="15">
-        <v>47.368421052631</v>
+        <v>78.125</v>
       </c>
       <c r="I17" s="14">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="J17" s="14">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K17" s="15">
-        <v>20</v>
+        <v>30.701754385964</v>
       </c>
       <c r="L17" s="15">
-        <v>18.918918918918</v>
+        <v>30.701754385964</v>
       </c>
       <c r="M17" s="15">
-        <v>97.014925373134</v>
+        <v>109.859154929577</v>
       </c>
       <c r="N17" s="15">
-        <v>100</v>
+        <v>109.859154929577</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-26.315789473684</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I18" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J18" s="14">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K18" s="15">
-        <v>-39.024390243902</v>
+        <v>-37.647058823529</v>
       </c>
       <c r="L18" s="15">
-        <v>2.040816326530</v>
+        <v>6</v>
       </c>
       <c r="M18" s="15">
-        <v>-38.271604938271</v>
+        <v>-39.772727272727</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.372093023255</v>
+        <v>-88.402625820568</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>-7.692307692307</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F19" s="14">
+        <v>53</v>
+      </c>
+      <c r="G19" s="14">
         <v>58</v>
       </c>
-      <c r="G19" s="14">
-        <v>61</v>
-      </c>
       <c r="H19" s="15">
-        <v>-4.918032786885</v>
+        <v>-8.620689655172</v>
       </c>
       <c r="I19" s="14">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="J19" s="14">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="K19" s="15">
-        <v>-20.197044334975</v>
+        <v>-19.158878504672</v>
       </c>
       <c r="L19" s="15">
-        <v>-38.167938931297</v>
+        <v>-37.545126353790</v>
       </c>
       <c r="M19" s="15">
-        <v>105.063291139241</v>
+        <v>101.162790697674</v>
       </c>
       <c r="N19" s="15">
-        <v>14.893617021276</v>
+        <v>16.891891891891</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G20" s="14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H20" s="15">
-        <v>-32.352941176470</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="I20" s="14">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J20" s="14">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K20" s="15">
-        <v>-32.061068702290</v>
+        <v>-31.386861313868</v>
       </c>
       <c r="L20" s="15">
-        <v>-27.642276422764</v>
+        <v>-29.323308270676</v>
       </c>
       <c r="M20" s="15">
-        <v>50.847457627118</v>
+        <v>46.875</v>
       </c>
       <c r="N20" s="15">
-        <v>-80.044843049327</v>
+        <v>-80.375782881002</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D21" s="17">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>19.047619047619</v>
+        <v>30</v>
       </c>
       <c r="F21" s="17">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G21" s="17">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="H21" s="18">
-        <v>11.445783132530</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I21" s="17">
-        <v>532</v>
+        <v>575</v>
       </c>
       <c r="J21" s="17">
-        <v>599</v>
+        <v>629</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.185308848080</v>
+        <v>-8.585055643879</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.555555555555</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="M21" s="18">
-        <v>43.783783783783</v>
+        <v>45.202020202020</v>
       </c>
       <c r="N21" s="18">
-        <v>-58.855375096674</v>
+        <v>-58.272859216255</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I22" s="14">
         <v>9</v>
@@ -1207,7 +1207,7 @@
         <v>80</v>
       </c>
       <c r="L22" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="15">
         <v>50</v>
@@ -1221,10 +1221,10 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
         <v>100</v>
@@ -1233,25 +1233,25 @@
         <v>15</v>
       </c>
       <c r="G23" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J23" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K23" s="15">
-        <v>30</v>
+        <v>32.258064516129</v>
       </c>
       <c r="L23" s="15">
-        <v>25.806451612903</v>
+        <v>20.588235294117</v>
       </c>
       <c r="M23" s="15">
-        <v>116.666666666667</v>
+        <v>127.777777777778</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>-18.518518518518</v>
+        <v>2.941176470588</v>
       </c>
       <c r="F24" s="14">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="G24" s="14">
         <v>126</v>
       </c>
       <c r="H24" s="15">
-        <v>-10.317460317460</v>
+        <v>-0.793650793650</v>
       </c>
       <c r="I24" s="14">
-        <v>382</v>
+        <v>419</v>
       </c>
       <c r="J24" s="14">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="K24" s="15">
-        <v>7.605633802816</v>
+        <v>7.712082262210</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.612440191387</v>
+        <v>-5.203619909502</v>
       </c>
       <c r="M24" s="15">
-        <v>71.300448430493</v>
+        <v>76.050420168067</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
         <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-11.111111111111</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G25" s="14">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H25" s="15">
-        <v>14.634146341463</v>
+        <v>35</v>
       </c>
       <c r="I25" s="14">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="J25" s="14">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K25" s="15">
-        <v>31.147540983606</v>
+        <v>35.114503816793</v>
       </c>
       <c r="L25" s="15">
-        <v>-16.666666666666</v>
+        <v>-11.5</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-5.263157894736</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
         <v>59</v>
       </c>
       <c r="G26" s="14">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H26" s="15">
-        <v>13.461538461538</v>
+        <v>28.260869565217</v>
       </c>
       <c r="I26" s="14">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="J26" s="14">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.994011976047</v>
+        <v>-3.351955307262</v>
       </c>
       <c r="L26" s="15">
-        <v>21.804511278195</v>
+        <v>20.979020979021</v>
       </c>
       <c r="M26" s="15">
-        <v>2.531645569620</v>
+        <v>-0.574712643678</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>55.555555555555</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>16.666666666666</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-14.285714285714</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I28" s="14">
         <v>20</v>
       </c>
       <c r="J28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>5.263157894736</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>25</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J29" s="14">
         <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-54.545454545454</v>
+        <v>-69.230769230769</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L30" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-50</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-049pct.xlsx
+++ b/data/source/weekly/cs-en-us-049pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>4</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-75</v>
       </c>
       <c r="F15" s="14">
         <v>4</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>114.285714285714</v>
+        <v>45.454545454545</v>
       </c>
       <c r="L15" s="15">
-        <v>15.384615384615</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="N15" s="15">
-        <v>150</v>
+        <v>166.666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>6</v>
+      </c>
+      <c r="D16" s="14">
         <v>5</v>
       </c>
-      <c r="D16" s="14">
-        <v>6</v>
-      </c>
       <c r="E16" s="15">
-        <v>-16.666666666666</v>
+        <v>20</v>
       </c>
       <c r="F16" s="14">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G16" s="14">
         <v>18</v>
       </c>
       <c r="H16" s="15">
-        <v>88.888888888888</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I16" s="14">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J16" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K16" s="15">
-        <v>28.571428571428</v>
+        <v>28</v>
       </c>
       <c r="L16" s="15">
-        <v>13.924050632911</v>
+        <v>10.344827586206</v>
       </c>
       <c r="M16" s="15">
-        <v>12.5</v>
+        <v>18.518518518518</v>
       </c>
       <c r="N16" s="15">
-        <v>-57.746478873239</v>
+        <v>-56.363636363636</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
         <v>57</v>
       </c>
       <c r="G17" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>78.125</v>
+        <v>96.551724137931</v>
       </c>
       <c r="I17" s="14">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="J17" s="14">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K17" s="15">
-        <v>30.701754385964</v>
+        <v>30.645161290322</v>
       </c>
       <c r="L17" s="15">
-        <v>30.701754385964</v>
+        <v>33.884297520661</v>
       </c>
       <c r="M17" s="15">
-        <v>109.859154929577</v>
+        <v>118.918918918919</v>
       </c>
       <c r="N17" s="15">
-        <v>109.859154929577</v>
+        <v>121.917808219178</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-23.529411764705</v>
+        <v>-12.5</v>
       </c>
       <c r="I18" s="14">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J18" s="14">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K18" s="15">
-        <v>-37.647058823529</v>
+        <v>-31.395348837209</v>
       </c>
       <c r="L18" s="15">
-        <v>6</v>
+        <v>15.686274509803</v>
       </c>
       <c r="M18" s="15">
-        <v>-39.772727272727</v>
+        <v>-36.559139784946</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.402625820568</v>
+        <v>-87.809917355371</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>-18.181818181818</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G19" s="14">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H19" s="15">
-        <v>-8.620689655172</v>
+        <v>-5.454545454545</v>
       </c>
       <c r="I19" s="14">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="J19" s="14">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="K19" s="15">
-        <v>-19.158878504672</v>
+        <v>-16.814159292035</v>
       </c>
       <c r="L19" s="15">
-        <v>-37.545126353790</v>
+        <v>-34.948096885813</v>
       </c>
       <c r="M19" s="15">
-        <v>101.162790697674</v>
+        <v>84.313725490196</v>
       </c>
       <c r="N19" s="15">
-        <v>16.891891891891</v>
+        <v>13.253012048192</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>-16.666666666666</v>
+        <v>-30</v>
       </c>
       <c r="F20" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G20" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H20" s="15">
-        <v>-27.586206896551</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I20" s="14">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="J20" s="14">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="K20" s="15">
-        <v>-31.386861313868</v>
+        <v>-31.292517006802</v>
       </c>
       <c r="L20" s="15">
-        <v>-29.323308270676</v>
+        <v>-26.277372262773</v>
       </c>
       <c r="M20" s="15">
-        <v>46.875</v>
+        <v>55.384615384615</v>
       </c>
       <c r="N20" s="15">
-        <v>-80.375782881002</v>
+        <v>-81.156716417910</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E21" s="18">
-        <v>30</v>
+        <v>4.761904761904</v>
       </c>
       <c r="F21" s="17">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G21" s="17">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H21" s="18">
-        <v>18.181818181818</v>
+        <v>15.483870967741</v>
       </c>
       <c r="I21" s="17">
-        <v>575</v>
+        <v>623</v>
       </c>
       <c r="J21" s="17">
-        <v>629</v>
+        <v>671</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.585055643879</v>
+        <v>-7.153502235469</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.793103448275</v>
+        <v>-10.872675250357</v>
       </c>
       <c r="M21" s="18">
-        <v>45.202020202020</v>
+        <v>47.630331753554</v>
       </c>
       <c r="N21" s="18">
-        <v>-58.272859216255</v>
+        <v>-58.159838817998</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>9</v>
@@ -1207,10 +1207,10 @@
         <v>80</v>
       </c>
       <c r="L22" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F23" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G23" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>66.666666666666</v>
+        <v>116.666666666667</v>
       </c>
       <c r="I23" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J23" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K23" s="15">
-        <v>32.258064516129</v>
+        <v>37.5</v>
       </c>
       <c r="L23" s="15">
-        <v>20.588235294117</v>
+        <v>18.918918918918</v>
       </c>
       <c r="M23" s="15">
-        <v>127.777777777778</v>
+        <v>131.578947368421</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>2.941176470588</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="14">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H24" s="15">
-        <v>-0.793650793650</v>
+        <v>-1.5625</v>
       </c>
       <c r="I24" s="14">
+        <v>444</v>
+      </c>
+      <c r="J24" s="14">
         <v>419</v>
       </c>
-      <c r="J24" s="14">
-        <v>389</v>
-      </c>
       <c r="K24" s="15">
-        <v>7.712082262210</v>
+        <v>5.966587112171</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.203619909502</v>
+        <v>-4.721030042918</v>
       </c>
       <c r="M24" s="15">
-        <v>76.050420168067</v>
+        <v>70.769230769230</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>66.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F25" s="14">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G25" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H25" s="15">
-        <v>35</v>
+        <v>24.390243902439</v>
       </c>
       <c r="I25" s="14">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J25" s="14">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="K25" s="15">
-        <v>35.114503816793</v>
+        <v>28.965517241379</v>
       </c>
       <c r="L25" s="15">
-        <v>-11.5</v>
+        <v>-9.223300970873</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G26" s="14">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>28.260869565217</v>
+        <v>45.238095238095</v>
       </c>
       <c r="I26" s="14">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="J26" s="14">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.351955307262</v>
+        <v>-0.534759358288</v>
       </c>
       <c r="L26" s="15">
-        <v>20.979020979021</v>
+        <v>22.368421052631</v>
       </c>
       <c r="M26" s="15">
-        <v>-0.574712643678</v>
+        <v>1.086956521739</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>4</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-75</v>
       </c>
       <c r="F27" s="14">
         <v>4</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>66.666666666666</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L27" s="15">
-        <v>7.142857142857</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-28.571428571428</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="L28" s="15">
-        <v>-4.761904761904</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-69.230769230769</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-70</v>
+        <v>-72.727272727272</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-049pct.xlsx
+++ b/data/source/weekly/cs-en-us-049pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>4</v>
-      </c>
       <c r="E15" s="15">
-        <v>-75</v>
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>45.454545454545</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>23.076923076923</v>
+        <v>38.461538461538</v>
       </c>
       <c r="M15" s="15">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>166.666666666667</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G16" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H16" s="15">
-        <v>55.555555555555</v>
+        <v>58.823529411764</v>
       </c>
       <c r="I16" s="14">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J16" s="14">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K16" s="15">
-        <v>28</v>
+        <v>31.168831168831</v>
       </c>
       <c r="L16" s="15">
-        <v>10.344827586206</v>
+        <v>7.446808510638</v>
       </c>
       <c r="M16" s="15">
-        <v>18.518518518518</v>
+        <v>16.091954022988</v>
       </c>
       <c r="N16" s="15">
-        <v>-56.363636363636</v>
+        <v>-57.916666666666</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
         <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F17" s="14">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G17" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H17" s="15">
-        <v>96.551724137931</v>
+        <v>87.878787878787</v>
       </c>
       <c r="I17" s="14">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="J17" s="14">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="K17" s="15">
-        <v>30.645161290322</v>
+        <v>32.089552238806</v>
       </c>
       <c r="L17" s="15">
-        <v>33.884297520661</v>
+        <v>38.28125</v>
       </c>
       <c r="M17" s="15">
-        <v>118.918918918919</v>
+        <v>126.923076923077</v>
       </c>
       <c r="N17" s="15">
-        <v>121.917808219178</v>
+        <v>121.25</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>500</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-12.5</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J18" s="14">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K18" s="15">
-        <v>-31.395348837209</v>
+        <v>-31.460674157303</v>
       </c>
       <c r="L18" s="15">
-        <v>15.686274509803</v>
+        <v>7.017543859649</v>
       </c>
       <c r="M18" s="15">
-        <v>-36.559139784946</v>
+        <v>-39</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.809917355371</v>
+        <v>-88.109161793372</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>16.666666666666</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F19" s="14">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G19" s="14">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.454545454545</v>
+        <v>-8.163265306122</v>
       </c>
       <c r="I19" s="14">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="J19" s="14">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.814159292035</v>
+        <v>-18.410041841004</v>
       </c>
       <c r="L19" s="15">
-        <v>-34.948096885813</v>
+        <v>-35.215946843853</v>
       </c>
       <c r="M19" s="15">
-        <v>84.313725490196</v>
+        <v>87.5</v>
       </c>
       <c r="N19" s="15">
-        <v>13.253012048192</v>
+        <v>14.705882352941</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
         <v>7</v>
       </c>
-      <c r="D20" s="14">
-        <v>10</v>
-      </c>
       <c r="E20" s="15">
-        <v>-30</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G20" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H20" s="15">
-        <v>-27.272727272727</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="I20" s="14">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J20" s="14">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="K20" s="15">
-        <v>-31.292517006802</v>
+        <v>-33.116883116883</v>
       </c>
       <c r="L20" s="15">
-        <v>-26.277372262773</v>
+        <v>-27.972027972028</v>
       </c>
       <c r="M20" s="15">
-        <v>55.384615384615</v>
+        <v>43.055555555555</v>
       </c>
       <c r="N20" s="15">
-        <v>-81.156716417910</v>
+        <v>-82.601351351351</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E21" s="18">
-        <v>4.761904761904</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F21" s="17">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G21" s="17">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H21" s="18">
-        <v>15.483870967741</v>
+        <v>16</v>
       </c>
       <c r="I21" s="17">
-        <v>623</v>
+        <v>656</v>
       </c>
       <c r="J21" s="17">
-        <v>671</v>
+        <v>707</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.153502235469</v>
+        <v>-7.213578500707</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.872675250357</v>
+        <v>-10.990502035278</v>
       </c>
       <c r="M21" s="18">
-        <v>47.630331753554</v>
+        <v>46.102449888641</v>
       </c>
       <c r="N21" s="18">
-        <v>-58.159838817998</v>
+        <v>-59.127725856697</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,14 +1188,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
-      </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>0</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>9</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
-      </c>
-      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="E23" s="15">
-        <v>200</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>116.666666666667</v>
+        <v>150</v>
       </c>
       <c r="I23" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J23" s="14">
         <v>32</v>
       </c>
       <c r="K23" s="15">
-        <v>37.5</v>
+        <v>40.625</v>
       </c>
       <c r="L23" s="15">
-        <v>18.918918918918</v>
+        <v>18.421052631578</v>
       </c>
       <c r="M23" s="15">
-        <v>131.578947368421</v>
+        <v>125</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>-13.333333333333</v>
+        <v>40</v>
       </c>
       <c r="F24" s="14">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G24" s="14">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.5625</v>
+        <v>3.448275862068</v>
       </c>
       <c r="I24" s="14">
+        <v>480</v>
+      </c>
+      <c r="J24" s="14">
         <v>444</v>
       </c>
-      <c r="J24" s="14">
-        <v>419</v>
-      </c>
       <c r="K24" s="15">
-        <v>5.966587112171</v>
+        <v>8.108108108108</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.721030042918</v>
+        <v>0.208768267223</v>
       </c>
       <c r="M24" s="15">
-        <v>70.769230769230</v>
+        <v>73.913043478260</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>15</v>
+      </c>
+      <c r="D25" s="14">
         <v>10</v>
       </c>
-      <c r="D25" s="14">
-        <v>14</v>
-      </c>
       <c r="E25" s="15">
-        <v>-28.571428571428</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G25" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H25" s="15">
-        <v>24.390243902439</v>
+        <v>19.047619047619</v>
       </c>
       <c r="I25" s="14">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="J25" s="14">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="K25" s="15">
-        <v>28.965517241379</v>
+        <v>30.322580645161</v>
       </c>
       <c r="L25" s="15">
-        <v>-9.223300970873</v>
+        <v>-4.265402843601</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="G26" s="14">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H26" s="15">
-        <v>45.238095238095</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J26" s="14">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="K26" s="15">
-        <v>-0.534759358288</v>
+        <v>-6.930693069306</v>
       </c>
       <c r="L26" s="15">
-        <v>22.368421052631</v>
+        <v>18.987341772151</v>
       </c>
       <c r="M26" s="15">
-        <v>1.086956521739</v>
+        <v>-5.050505050505</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J27" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>23.076923076923</v>
+        <v>20</v>
       </c>
       <c r="L27" s="15">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
@@ -1444,16 +1444,16 @@
         <v>-50</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J28" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>-9.523809523809</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L28" s="15">
-        <v>-9.523809523809</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="14">
         <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-71.428571428571</v>
+        <v>-68.75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-72.727272727272</v>
+        <v>-69.230769230769</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-049pct.xlsx
+++ b/data/source/weekly/cs-en-us-049pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -892,38 +892,38 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>18</v>
       </c>
       <c r="J15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>38.461538461538</v>
       </c>
       <c r="L15" s="15">
         <v>38.461538461538</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="N15" s="15">
         <v>200</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F16" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G16" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>58.823529411764</v>
+        <v>56.25</v>
       </c>
       <c r="I16" s="14">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="J16" s="14">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K16" s="15">
-        <v>31.168831168831</v>
+        <v>37.5</v>
       </c>
       <c r="L16" s="15">
-        <v>7.446808510638</v>
+        <v>15.789473684210</v>
       </c>
       <c r="M16" s="15">
-        <v>16.091954022988</v>
+        <v>20.879120879120</v>
       </c>
       <c r="N16" s="15">
-        <v>-57.916666666666</v>
+        <v>-57.03125</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>10</v>
+      </c>
+      <c r="D17" s="14">
         <v>13</v>
       </c>
-      <c r="D17" s="14">
-        <v>10</v>
-      </c>
       <c r="E17" s="15">
-        <v>30</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F17" s="14">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G17" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H17" s="15">
-        <v>87.878787878787</v>
+        <v>45.945945945945</v>
       </c>
       <c r="I17" s="14">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="J17" s="14">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="K17" s="15">
-        <v>32.089552238806</v>
+        <v>26.530612244898</v>
       </c>
       <c r="L17" s="15">
-        <v>38.28125</v>
+        <v>32.857142857142</v>
       </c>
       <c r="M17" s="15">
-        <v>126.923076923077</v>
+        <v>113.793103448276</v>
       </c>
       <c r="N17" s="15">
-        <v>121.25</v>
+        <v>113.793103448276</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>60</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-13.333333333333</v>
+        <v>58.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="J18" s="14">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="K18" s="15">
-        <v>-31.460674157303</v>
+        <v>-26.595744680851</v>
       </c>
       <c r="L18" s="15">
-        <v>7.017543859649</v>
+        <v>13.114754098360</v>
       </c>
       <c r="M18" s="15">
-        <v>-39</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.109161793372</v>
+        <v>-87.431693989071</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E19" s="15">
-        <v>-23.076923076923</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F19" s="14">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G19" s="14">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H19" s="15">
-        <v>-8.163265306122</v>
+        <v>-29.824561403508</v>
       </c>
       <c r="I19" s="14">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="J19" s="14">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.410041841004</v>
+        <v>-21.538461538461</v>
       </c>
       <c r="L19" s="15">
-        <v>-35.215946843853</v>
+        <v>-36.645962732919</v>
       </c>
       <c r="M19" s="15">
-        <v>87.5</v>
+        <v>82.142857142857</v>
       </c>
       <c r="N19" s="15">
-        <v>14.705882352941</v>
+        <v>9.677419354838</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-57.142857142857</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F20" s="14">
         <v>22</v>
       </c>
       <c r="G20" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H20" s="15">
-        <v>-29.032258064516</v>
+        <v>-31.25</v>
       </c>
       <c r="I20" s="14">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="J20" s="14">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="K20" s="15">
-        <v>-33.116883116883</v>
+        <v>-31.901840490797</v>
       </c>
       <c r="L20" s="15">
-        <v>-27.972027972028</v>
+        <v>-27.450980392156</v>
       </c>
       <c r="M20" s="15">
-        <v>43.055555555555</v>
+        <v>42.307692307692</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.601351351351</v>
+        <v>-82.380952380952</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E21" s="18">
-        <v>-5.555555555555</v>
+        <v>-17.307692307692</v>
       </c>
       <c r="F21" s="17">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="G21" s="17">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="H21" s="18">
-        <v>16</v>
+        <v>2.5</v>
       </c>
       <c r="I21" s="17">
-        <v>656</v>
+        <v>699</v>
       </c>
       <c r="J21" s="17">
-        <v>707</v>
+        <v>759</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.213578500707</v>
+        <v>-7.905138339920</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.990502035278</v>
+        <v>-10.955414012738</v>
       </c>
       <c r="M21" s="18">
-        <v>46.102449888641</v>
+        <v>45.625</v>
       </c>
       <c r="N21" s="18">
-        <v>-59.127725856697</v>
+        <v>-59.313154831199</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
         <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I23" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J23" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K23" s="15">
-        <v>40.625</v>
+        <v>38.235294117647</v>
       </c>
       <c r="L23" s="15">
-        <v>18.421052631578</v>
+        <v>9.302325581395</v>
       </c>
       <c r="M23" s="15">
-        <v>125</v>
+        <v>123.809523809524</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E24" s="15">
-        <v>40</v>
+        <v>-36.585365853658</v>
       </c>
       <c r="F24" s="14">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G24" s="14">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="H24" s="15">
-        <v>3.448275862068</v>
+        <v>-5.384615384615</v>
       </c>
       <c r="I24" s="14">
-        <v>480</v>
+        <v>507</v>
       </c>
       <c r="J24" s="14">
-        <v>444</v>
+        <v>485</v>
       </c>
       <c r="K24" s="15">
-        <v>8.108108108108</v>
+        <v>4.536082474226</v>
       </c>
       <c r="L24" s="15">
-        <v>0.208768267223</v>
+        <v>0.197628458498</v>
       </c>
       <c r="M24" s="15">
-        <v>73.913043478260</v>
+        <v>77.894736842105</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="F25" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G25" s="14">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H25" s="15">
-        <v>19.047619047619</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="J25" s="14">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="K25" s="15">
-        <v>30.322580645161</v>
+        <v>23.121387283237</v>
       </c>
       <c r="L25" s="15">
-        <v>-4.265402843601</v>
+        <v>-1.843317972350</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>-66.666666666666</v>
+        <v>-43.75</v>
       </c>
       <c r="F26" s="14">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G26" s="14">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H26" s="15">
-        <v>-16.666666666666</v>
+        <v>-25.490196078431</v>
       </c>
       <c r="I26" s="14">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="J26" s="14">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.930693069306</v>
+        <v>-9.174311926605</v>
       </c>
       <c r="L26" s="15">
-        <v>18.987341772151</v>
+        <v>17.857142857142</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.050505050505</v>
+        <v>-7.476635514018</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H27" s="15">
-        <v>-16.666666666666</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I27" s="14">
         <v>18</v>
       </c>
       <c r="J27" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K27" s="15">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="L27" s="15">
-        <v>28.571428571428</v>
+        <v>20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,31 +1426,31 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
         <v>3</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I28" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J28" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K28" s="15">
-        <v>-4.347826086956</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="L28" s="15">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M29" s="15">
         <v>-16.666666666666</v>
@@ -1535,7 +1535,7 @@
         <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
         <v>-33.333333333333</v>

--- a/data/source/weekly/cs-en-us-049pct.xlsx
+++ b/data/source/weekly/cs-en-us-049pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -885,7 +885,7 @@
         <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>18</v>
@@ -923,10 +923,10 @@
         <v>38.461538461538</v>
       </c>
       <c r="M15" s="15">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="N15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>166.666666666667</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G16" s="14">
         <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>56.25</v>
+        <v>37.5</v>
       </c>
       <c r="I16" s="14">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J16" s="14">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K16" s="15">
-        <v>37.5</v>
+        <v>30.232558139534</v>
       </c>
       <c r="L16" s="15">
-        <v>15.789473684210</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M16" s="15">
-        <v>20.879120879120</v>
+        <v>15.463917525773</v>
       </c>
       <c r="N16" s="15">
-        <v>-57.03125</v>
+        <v>-57.894736842105</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>-23.076923076923</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G17" s="14">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H17" s="15">
-        <v>45.945945945945</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="J17" s="14">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="K17" s="15">
-        <v>26.530612244898</v>
+        <v>28.301886792452</v>
       </c>
       <c r="L17" s="15">
-        <v>32.857142857142</v>
+        <v>30.769230769230</v>
       </c>
       <c r="M17" s="15">
-        <v>113.793103448276</v>
+        <v>121.739130434783</v>
       </c>
       <c r="N17" s="15">
-        <v>113.793103448276</v>
+        <v>117.021276595745</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>60</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
         <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>58.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I18" s="14">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J18" s="14">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K18" s="15">
-        <v>-26.595744680851</v>
+        <v>-26.804123711340</v>
       </c>
       <c r="L18" s="15">
-        <v>13.114754098360</v>
+        <v>5.970149253731</v>
       </c>
       <c r="M18" s="15">
-        <v>-32.352941176470</v>
+        <v>-35.454545454545</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.431693989071</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>-57.142857142857</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F19" s="14">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G19" s="14">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H19" s="15">
-        <v>-29.824561403508</v>
+        <v>-29.230769230769</v>
       </c>
       <c r="I19" s="14">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="J19" s="14">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="K19" s="15">
-        <v>-21.538461538461</v>
+        <v>-21.146953405017</v>
       </c>
       <c r="L19" s="15">
-        <v>-36.645962732919</v>
+        <v>-34.328358208955</v>
       </c>
       <c r="M19" s="15">
-        <v>82.142857142857</v>
+        <v>76</v>
       </c>
       <c r="N19" s="15">
-        <v>9.677419354838</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E20" s="15">
-        <v>-11.111111111111</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G20" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H20" s="15">
-        <v>-31.25</v>
+        <v>-44.736842105263</v>
       </c>
       <c r="I20" s="14">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J20" s="14">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="K20" s="15">
-        <v>-31.901840490797</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>-27.450980392156</v>
+        <v>-29.012345679012</v>
       </c>
       <c r="M20" s="15">
-        <v>42.307692307692</v>
+        <v>40.243902439024</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.380952380952</v>
+        <v>-82.602118003025</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
         <v>52</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.307692307692</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="F21" s="17">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G21" s="17">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="H21" s="18">
-        <v>2.5</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="I21" s="17">
-        <v>699</v>
+        <v>741</v>
       </c>
       <c r="J21" s="17">
-        <v>759</v>
+        <v>811</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.905138339920</v>
+        <v>-8.631319358816</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.955414012738</v>
+        <v>-10.9375</v>
       </c>
       <c r="M21" s="18">
-        <v>45.625</v>
+        <v>43.050193050193</v>
       </c>
       <c r="N21" s="18">
-        <v>-59.313154831199</v>
+        <v>-58.901830282861</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
         <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I23" s="14">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J23" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K23" s="15">
-        <v>38.235294117647</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>9.302325581395</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M23" s="15">
-        <v>123.809523809524</v>
+        <v>118.181818181818</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D24" s="14">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E24" s="15">
-        <v>-36.585365853658</v>
+        <v>2.564102564102</v>
       </c>
       <c r="F24" s="14">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G24" s="14">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.384615384615</v>
+        <v>-4.444444444444</v>
       </c>
       <c r="I24" s="14">
-        <v>507</v>
+        <v>547</v>
       </c>
       <c r="J24" s="14">
-        <v>485</v>
+        <v>524</v>
       </c>
       <c r="K24" s="15">
-        <v>4.536082474226</v>
+        <v>4.389312977099</v>
       </c>
       <c r="L24" s="15">
-        <v>0.197628458498</v>
+        <v>3.402646502835</v>
       </c>
       <c r="M24" s="15">
-        <v>77.894736842105</v>
+        <v>79.934210526315</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>-38.888888888888</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G25" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>-9.259259259259</v>
       </c>
       <c r="I25" s="14">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="J25" s="14">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="K25" s="15">
-        <v>23.121387283237</v>
+        <v>22.162162162162</v>
       </c>
       <c r="L25" s="15">
-        <v>-1.843317972350</v>
+        <v>0.444444444444</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>-43.75</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F26" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G26" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H26" s="15">
-        <v>-25.490196078431</v>
+        <v>-25</v>
       </c>
       <c r="I26" s="14">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="J26" s="14">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.174311926605</v>
+        <v>-9.787234042553</v>
       </c>
       <c r="L26" s="15">
-        <v>17.857142857142</v>
+        <v>19.774011299435</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.476635514018</v>
+        <v>-6.607929515418</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>7</v>
       </c>
       <c r="H27" s="15">
-        <v>-42.857142857142</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I27" s="14">
         <v>18</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-66.666666666666</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-42.857142857142</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J28" s="14">
         <v>26</v>
       </c>
       <c r="K28" s="15">
-        <v>-11.538461538461</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>4.166666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
